--- a/artfynd/A 53705-2025 artfynd.xlsx
+++ b/artfynd/A 53705-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129513684</v>
+        <v>129508216</v>
       </c>
       <c r="B2" t="n">
-        <v>96962</v>
+        <v>91848</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,27 +686,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -714,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481077</v>
+        <v>481273</v>
       </c>
       <c r="R2" t="n">
-        <v>6782765</v>
+        <v>6782732</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -747,14 +750,19 @@
           <t>2025-11-03</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-03</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>sparsamt</t>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,17 +783,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129508216</v>
+        <v>129513684</v>
       </c>
       <c r="B3" t="n">
-        <v>91847</v>
+        <v>96970</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,30 +801,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -824,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481273</v>
+        <v>481077</v>
       </c>
       <c r="R3" t="n">
-        <v>6782732</v>
+        <v>6782765</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,19 +862,14 @@
           <t>2025-11-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-03</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:25</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>sparsamt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,7 +890,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1372,7 +1372,7 @@
         <v>129508399</v>
       </c>
       <c r="B8" t="n">
-        <v>95954</v>
+        <v>95962</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>129508184</v>
       </c>
       <c r="B9" t="n">
-        <v>95954</v>
+        <v>95962</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>129506853</v>
       </c>
       <c r="B10" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>129508251</v>
       </c>
       <c r="B11" t="n">
-        <v>92002</v>
+        <v>92003</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,6 +1808,332 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129519225</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91550</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Unnån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>481149</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6782776</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På en granlåga</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129519240</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Unnån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>481152</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6782751</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre hack i torrtall</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129519249</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Unnån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>481184</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6782769</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre hack i granlåga</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53705-2025 artfynd.xlsx
+++ b/artfynd/A 53705-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129508216</v>
+        <v>129513684</v>
       </c>
       <c r="B2" t="n">
-        <v>91848</v>
+        <v>96970</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,30 +686,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -717,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481273</v>
+        <v>481077</v>
       </c>
       <c r="R2" t="n">
-        <v>6782732</v>
+        <v>6782765</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,19 +747,14 @@
           <t>2025-11-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-03</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:25</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>sparsamt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,17 +775,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129513684</v>
+        <v>129508216</v>
       </c>
       <c r="B3" t="n">
-        <v>96970</v>
+        <v>91848</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,27 +793,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481077</v>
+        <v>481273</v>
       </c>
       <c r="R3" t="n">
-        <v>6782765</v>
+        <v>6782732</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,14 +857,19 @@
           <t>2025-11-03</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-03</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>sparsamt</t>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,7 +890,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 53705-2025 artfynd.xlsx
+++ b/artfynd/A 53705-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129513684</v>
       </c>
       <c r="B2" t="n">
-        <v>96970</v>
+        <v>96973</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129508216</v>
       </c>
       <c r="B3" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1372,7 +1372,7 @@
         <v>129508399</v>
       </c>
       <c r="B8" t="n">
-        <v>95962</v>
+        <v>95965</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>129508184</v>
       </c>
       <c r="B9" t="n">
-        <v>95962</v>
+        <v>95965</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>129506853</v>
       </c>
       <c r="B10" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>129508251</v>
       </c>
       <c r="B11" t="n">
-        <v>92003</v>
+        <v>92006</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>129519225</v>
       </c>
       <c r="B12" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 53705-2025 artfynd.xlsx
+++ b/artfynd/A 53705-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129513684</v>
+        <v>129508216</v>
       </c>
       <c r="B2" t="n">
-        <v>96973</v>
+        <v>91851</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,27 +686,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -714,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481077</v>
+        <v>481273</v>
       </c>
       <c r="R2" t="n">
-        <v>6782765</v>
+        <v>6782732</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -747,14 +750,19 @@
           <t>2025-11-03</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-03</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>sparsamt</t>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,17 +783,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129508216</v>
+        <v>129513684</v>
       </c>
       <c r="B3" t="n">
-        <v>91851</v>
+        <v>96973</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,30 +801,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -824,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481273</v>
+        <v>481077</v>
       </c>
       <c r="R3" t="n">
-        <v>6782732</v>
+        <v>6782765</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,19 +862,14 @@
           <t>2025-11-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-03</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:25</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>sparsamt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,7 +890,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer, Peter Turander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer, Peter Turander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 53705-2025 artfynd.xlsx
+++ b/artfynd/A 53705-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129508216</v>
+        <v>129513684</v>
       </c>
       <c r="B2" t="n">
-        <v>91851</v>
+        <v>96973</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,30 +686,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -717,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481273</v>
+        <v>481077</v>
       </c>
       <c r="R2" t="n">
-        <v>6782732</v>
+        <v>6782765</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,19 +747,14 @@
           <t>2025-11-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-03</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:25</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>sparsamt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,17 +775,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129513684</v>
+        <v>129508216</v>
       </c>
       <c r="B3" t="n">
-        <v>96973</v>
+        <v>91851</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,27 +793,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481077</v>
+        <v>481273</v>
       </c>
       <c r="R3" t="n">
-        <v>6782765</v>
+        <v>6782732</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,14 +857,19 @@
           <t>2025-11-03</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-03</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>sparsamt</t>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,7 +890,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer, Peter Turander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer, Peter Turander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 53705-2025 artfynd.xlsx
+++ b/artfynd/A 53705-2025 artfynd.xlsx
@@ -1474,7 +1474,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 53705-2025 artfynd.xlsx
+++ b/artfynd/A 53705-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129513684</v>
       </c>
       <c r="B2" t="n">
-        <v>96973</v>
+        <v>97002</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129508216</v>
       </c>
       <c r="B3" t="n">
-        <v>91851</v>
+        <v>91879</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>129506439</v>
       </c>
       <c r="B4" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>129507295</v>
       </c>
       <c r="B7" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>129508399</v>
       </c>
       <c r="B8" t="n">
-        <v>95965</v>
+        <v>95994</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>129508184</v>
       </c>
       <c r="B9" t="n">
-        <v>95965</v>
+        <v>95994</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>129506853</v>
       </c>
       <c r="B10" t="n">
-        <v>91851</v>
+        <v>91879</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>129508251</v>
       </c>
       <c r="B11" t="n">
-        <v>92006</v>
+        <v>92034</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>129519225</v>
       </c>
       <c r="B12" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>129519240</v>
       </c>
       <c r="B13" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>129519249</v>
       </c>
       <c r="B14" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 53705-2025 artfynd.xlsx
+++ b/artfynd/A 53705-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129513684</v>
       </c>
       <c r="B2" t="n">
-        <v>97002</v>
+        <v>97014</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129508216</v>
       </c>
       <c r="B3" t="n">
-        <v>91879</v>
+        <v>91885</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>129506439</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1251,7 +1251,7 @@
         <v>129507295</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>129508399</v>
       </c>
       <c r="B8" t="n">
-        <v>95994</v>
+        <v>96006</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>129508184</v>
       </c>
       <c r="B9" t="n">
-        <v>95994</v>
+        <v>96006</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>129506853</v>
       </c>
       <c r="B10" t="n">
-        <v>91879</v>
+        <v>91885</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>129508251</v>
       </c>
       <c r="B11" t="n">
-        <v>92034</v>
+        <v>92040</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>129519225</v>
       </c>
       <c r="B12" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>129519240</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>129519249</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 53705-2025 artfynd.xlsx
+++ b/artfynd/A 53705-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129513684</v>
       </c>
       <c r="B2" t="n">
-        <v>97014</v>
+        <v>97015</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129508216</v>
       </c>
       <c r="B3" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>129506439</v>
       </c>
       <c r="B4" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>129507295</v>
       </c>
       <c r="B7" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>129508399</v>
       </c>
       <c r="B8" t="n">
-        <v>96006</v>
+        <v>96007</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>129508184</v>
       </c>
       <c r="B9" t="n">
-        <v>96006</v>
+        <v>96007</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>129506853</v>
       </c>
       <c r="B10" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>129508251</v>
       </c>
       <c r="B11" t="n">
-        <v>92040</v>
+        <v>92041</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>129519225</v>
       </c>
       <c r="B12" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>129519240</v>
       </c>
       <c r="B13" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>129519249</v>
       </c>
       <c r="B14" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 53705-2025 artfynd.xlsx
+++ b/artfynd/A 53705-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129513684</v>
+        <v>129508216</v>
       </c>
       <c r="B2" t="n">
-        <v>97015</v>
+        <v>91891</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,27 +686,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -714,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481077</v>
+        <v>481273</v>
       </c>
       <c r="R2" t="n">
-        <v>6782765</v>
+        <v>6782732</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -747,14 +750,19 @@
           <t>2025-11-03</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-03</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>sparsamt</t>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,17 +783,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129508216</v>
+        <v>129513684</v>
       </c>
       <c r="B3" t="n">
-        <v>91886</v>
+        <v>97020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,30 +801,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -824,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481273</v>
+        <v>481077</v>
       </c>
       <c r="R3" t="n">
-        <v>6782732</v>
+        <v>6782765</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,19 +862,14 @@
           <t>2025-11-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-03</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:25</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>sparsamt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,7 +890,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1372,7 +1372,7 @@
         <v>129508399</v>
       </c>
       <c r="B8" t="n">
-        <v>96007</v>
+        <v>96012</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>129508184</v>
       </c>
       <c r="B9" t="n">
-        <v>96007</v>
+        <v>96012</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>129506853</v>
       </c>
       <c r="B10" t="n">
-        <v>91886</v>
+        <v>91891</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>129508251</v>
       </c>
       <c r="B11" t="n">
-        <v>92041</v>
+        <v>92046</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>129519225</v>
       </c>
       <c r="B12" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 53705-2025 artfynd.xlsx
+++ b/artfynd/A 53705-2025 artfynd.xlsx
@@ -1362,7 +1362,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 53705-2025 artfynd.xlsx
+++ b/artfynd/A 53705-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129508216</v>
+        <v>129513684</v>
       </c>
       <c r="B2" t="n">
-        <v>91891</v>
+        <v>97020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,30 +686,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -717,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481273</v>
+        <v>481077</v>
       </c>
       <c r="R2" t="n">
-        <v>6782732</v>
+        <v>6782765</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,19 +747,14 @@
           <t>2025-11-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-03</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:25</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>sparsamt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,17 +775,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129513684</v>
+        <v>129508216</v>
       </c>
       <c r="B3" t="n">
-        <v>97020</v>
+        <v>91891</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,27 +793,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481077</v>
+        <v>481273</v>
       </c>
       <c r="R3" t="n">
-        <v>6782765</v>
+        <v>6782732</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,14 +857,19 @@
           <t>2025-11-03</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-03</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>sparsamt</t>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,7 +890,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer, Peter Turander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer, Peter Turander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 53705-2025 artfynd.xlsx
+++ b/artfynd/A 53705-2025 artfynd.xlsx
@@ -1804,7 +1804,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 53705-2025 artfynd.xlsx
+++ b/artfynd/A 53705-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129513684</v>
       </c>
       <c r="B2" t="n">
-        <v>97020</v>
+        <v>97024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129508216</v>
       </c>
       <c r="B3" t="n">
-        <v>91891</v>
+        <v>91895</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>129508399</v>
       </c>
       <c r="B8" t="n">
-        <v>96012</v>
+        <v>96016</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>129508184</v>
       </c>
       <c r="B9" t="n">
-        <v>96012</v>
+        <v>96016</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>129506853</v>
       </c>
       <c r="B10" t="n">
-        <v>91891</v>
+        <v>91895</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>129508251</v>
       </c>
       <c r="B11" t="n">
-        <v>92046</v>
+        <v>92050</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1814,7 +1814,7 @@
         <v>129519225</v>
       </c>
       <c r="B12" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer, Peter Turander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 53705-2025 artfynd.xlsx
+++ b/artfynd/A 53705-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129513684</v>
+        <v>129508216</v>
       </c>
       <c r="B2" t="n">
-        <v>97024</v>
+        <v>91897</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,27 +686,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -714,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481077</v>
+        <v>481273</v>
       </c>
       <c r="R2" t="n">
-        <v>6782765</v>
+        <v>6782732</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -747,14 +750,19 @@
           <t>2025-11-03</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-03</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>sparsamt</t>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,17 +783,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129508216</v>
+        <v>129513684</v>
       </c>
       <c r="B3" t="n">
-        <v>91895</v>
+        <v>97026</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,30 +801,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -824,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481273</v>
+        <v>481077</v>
       </c>
       <c r="R3" t="n">
-        <v>6782732</v>
+        <v>6782765</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,19 +862,14 @@
           <t>2025-11-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-03</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:25</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>sparsamt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,7 +890,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1372,7 +1372,7 @@
         <v>129508399</v>
       </c>
       <c r="B8" t="n">
-        <v>96016</v>
+        <v>96018</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>129508184</v>
       </c>
       <c r="B9" t="n">
-        <v>96016</v>
+        <v>96018</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>129506853</v>
       </c>
       <c r="B10" t="n">
-        <v>91895</v>
+        <v>91897</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>129508251</v>
       </c>
       <c r="B11" t="n">
-        <v>92050</v>
+        <v>92052</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>129519225</v>
       </c>
       <c r="B12" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer, Peter Turander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer, Peter Turander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer, Peter Turander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 53705-2025 artfynd.xlsx
+++ b/artfynd/A 53705-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129508216</v>
+        <v>129513684</v>
       </c>
       <c r="B2" t="n">
-        <v>91897</v>
+        <v>97036</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,30 +686,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -717,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481273</v>
+        <v>481077</v>
       </c>
       <c r="R2" t="n">
-        <v>6782732</v>
+        <v>6782765</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,19 +747,14 @@
           <t>2025-11-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-03</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:25</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>sparsamt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,17 +775,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129513684</v>
+        <v>129508216</v>
       </c>
       <c r="B3" t="n">
-        <v>97026</v>
+        <v>91897</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,27 +793,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481077</v>
+        <v>481273</v>
       </c>
       <c r="R3" t="n">
-        <v>6782765</v>
+        <v>6782732</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,14 +857,19 @@
           <t>2025-11-03</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-03</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>sparsamt</t>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,7 +890,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1372,7 +1372,7 @@
         <v>129508399</v>
       </c>
       <c r="B8" t="n">
-        <v>96018</v>
+        <v>96028</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>129508184</v>
       </c>
       <c r="B9" t="n">
-        <v>96018</v>
+        <v>96028</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
